--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y875"/>
+  <dimension ref="A1:Y876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50534,14 +50534,14 @@
     <row r="848" ht="15" customHeight="1">
       <c r="A848" t="inlineStr">
         <is>
-          <t>A 55035-2023</t>
+          <t>A 55024-2023</t>
         </is>
       </c>
       <c r="B848" s="1" t="n">
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         </is>
       </c>
       <c r="G848" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -50591,14 +50591,14 @@
     <row r="849" ht="15" customHeight="1">
       <c r="A849" t="inlineStr">
         <is>
-          <t>A 55024-2023</t>
+          <t>A 55032-2023</t>
         </is>
       </c>
       <c r="B849" s="1" t="n">
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         </is>
       </c>
       <c r="G849" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -50648,14 +50648,14 @@
     <row r="850" ht="15" customHeight="1">
       <c r="A850" t="inlineStr">
         <is>
-          <t>A 55040-2023</t>
+          <t>A 55035-2023</t>
         </is>
       </c>
       <c r="B850" s="1" t="n">
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         </is>
       </c>
       <c r="G850" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -50705,14 +50705,14 @@
     <row r="851" ht="15" customHeight="1">
       <c r="A851" t="inlineStr">
         <is>
-          <t>A 55032-2023</t>
+          <t>A 55040-2023</t>
         </is>
       </c>
       <c r="B851" s="1" t="n">
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         </is>
       </c>
       <c r="G851" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50901,14 +50901,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 54114-2023</t>
+          <t>A 54125-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -50958,14 +50958,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 54118-2023</t>
+          <t>A 54114-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51015,14 +51015,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 54125-2023</t>
+          <t>A 54118-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51072,14 +51072,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 55556-2023</t>
+          <t>A 55550-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -51129,14 +51129,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 55550-2023</t>
+          <t>A 55556-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>9.9</v>
+        <v>1.3</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -51186,14 +51186,14 @@
     <row r="859" ht="15" customHeight="1">
       <c r="A859" t="inlineStr">
         <is>
-          <t>A 56064-2023</t>
+          <t>A 56057-2023</t>
         </is>
       </c>
       <c r="B859" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 56057-2023</t>
+          <t>A 56064-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
       </c>
       <c r="R874" s="2" t="inlineStr"/>
     </row>
-    <row r="875">
+    <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
           <t>A 59713-2023</t>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52151,6 +52151,63 @@
         <v>0</v>
       </c>
       <c r="R875" s="2" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>A 60249-2023</t>
+        </is>
+      </c>
+      <c r="B876" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C876" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>SALA</t>
+        </is>
+      </c>
+      <c r="G876" t="n">
+        <v>2</v>
+      </c>
+      <c r="H876" t="n">
+        <v>0</v>
+      </c>
+      <c r="I876" t="n">
+        <v>0</v>
+      </c>
+      <c r="J876" t="n">
+        <v>0</v>
+      </c>
+      <c r="K876" t="n">
+        <v>0</v>
+      </c>
+      <c r="L876" t="n">
+        <v>0</v>
+      </c>
+      <c r="M876" t="n">
+        <v>0</v>
+      </c>
+      <c r="N876" t="n">
+        <v>0</v>
+      </c>
+      <c r="O876" t="n">
+        <v>0</v>
+      </c>
+      <c r="P876" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q876" t="n">
+        <v>0</v>
+      </c>
+      <c r="R876" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50762,14 +50762,14 @@
     <row r="852" ht="15" customHeight="1">
       <c r="A852" t="inlineStr">
         <is>
-          <t>A 53877-2023</t>
+          <t>A 53951-2023</t>
         </is>
       </c>
       <c r="B852" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50781,8 +50781,13 @@
           <t>SALA</t>
         </is>
       </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G852" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -50815,18 +50820,38 @@
         <v>0</v>
       </c>
       <c r="R852" s="2" t="inlineStr"/>
+      <c r="U852">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1981/knärot/A 53951-2023 karta knärot.png", "A 53951-2023")</f>
+        <v/>
+      </c>
+      <c r="V852">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1981/klagomål/A 53951-2023 FSC-klagomål.docx", "A 53951-2023")</f>
+        <v/>
+      </c>
+      <c r="W852">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1981/klagomålsmail/A 53951-2023 FSC-klagomål mail.docx", "A 53951-2023")</f>
+        <v/>
+      </c>
+      <c r="X852">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1981/tillsyn/A 53951-2023 tillsynsbegäran.docx", "A 53951-2023")</f>
+        <v/>
+      </c>
+      <c r="Y852">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1981/tillsynsmail/A 53951-2023 tillsynsbegäran mail.docx", "A 53951-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="853" ht="15" customHeight="1">
       <c r="A853" t="inlineStr">
         <is>
-          <t>A 53951-2023</t>
+          <t>A 53877-2023</t>
         </is>
       </c>
       <c r="B853" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50838,13 +50863,8 @@
           <t>SALA</t>
         </is>
       </c>
-      <c r="F853" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G853" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -50877,38 +50897,18 @@
         <v>0</v>
       </c>
       <c r="R853" s="2" t="inlineStr"/>
-      <c r="U853">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1981/knärot/A 53951-2023 karta knärot.png", "A 53951-2023")</f>
-        <v/>
-      </c>
-      <c r="V853">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1981/klagomål/A 53951-2023 FSC-klagomål.docx", "A 53951-2023")</f>
-        <v/>
-      </c>
-      <c r="W853">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1981/klagomålsmail/A 53951-2023 FSC-klagomål mail.docx", "A 53951-2023")</f>
-        <v/>
-      </c>
-      <c r="X853">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1981/tillsyn/A 53951-2023 tillsynsbegäran.docx", "A 53951-2023")</f>
-        <v/>
-      </c>
-      <c r="Y853">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1981/tillsynsmail/A 53951-2023 tillsynsbegäran mail.docx", "A 53951-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 54125-2023</t>
+          <t>A 54114-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -50958,14 +50958,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 54114-2023</t>
+          <t>A 54118-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51015,14 +51015,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 54118-2023</t>
+          <t>A 54125-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51072,14 +51072,14 @@
     <row r="857" ht="15" customHeight="1">
       <c r="A857" t="inlineStr">
         <is>
-          <t>A 55550-2023</t>
+          <t>A 55556-2023</t>
         </is>
       </c>
       <c r="B857" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         </is>
       </c>
       <c r="G857" t="n">
-        <v>9.9</v>
+        <v>1.3</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -51129,14 +51129,14 @@
     <row r="858" ht="15" customHeight="1">
       <c r="A858" t="inlineStr">
         <is>
-          <t>A 55556-2023</t>
+          <t>A 55550-2023</t>
         </is>
       </c>
       <c r="B858" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         </is>
       </c>
       <c r="G858" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -51186,14 +51186,14 @@
     <row r="859" ht="15" customHeight="1">
       <c r="A859" t="inlineStr">
         <is>
-          <t>A 56057-2023</t>
+          <t>A 56064-2023</t>
         </is>
       </c>
       <c r="B859" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 56064-2023</t>
+          <t>A 56057-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50762,14 +50762,14 @@
     <row r="852" ht="15" customHeight="1">
       <c r="A852" t="inlineStr">
         <is>
-          <t>A 53951-2023</t>
+          <t>A 53877-2023</t>
         </is>
       </c>
       <c r="B852" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50781,123 +50781,123 @@
           <t>SALA</t>
         </is>
       </c>
-      <c r="F852" t="inlineStr">
+      <c r="G852" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H852" t="n">
+        <v>0</v>
+      </c>
+      <c r="I852" t="n">
+        <v>0</v>
+      </c>
+      <c r="J852" t="n">
+        <v>0</v>
+      </c>
+      <c r="K852" t="n">
+        <v>0</v>
+      </c>
+      <c r="L852" t="n">
+        <v>0</v>
+      </c>
+      <c r="M852" t="n">
+        <v>0</v>
+      </c>
+      <c r="N852" t="n">
+        <v>0</v>
+      </c>
+      <c r="O852" t="n">
+        <v>0</v>
+      </c>
+      <c r="P852" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q852" t="n">
+        <v>0</v>
+      </c>
+      <c r="R852" s="2" t="inlineStr"/>
+    </row>
+    <row r="853" ht="15" customHeight="1">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>A 53951-2023</t>
+        </is>
+      </c>
+      <c r="B853" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="C853" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>SALA</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="G852" t="n">
+      <c r="G853" t="n">
         <v>8.4</v>
       </c>
-      <c r="H852" t="n">
-        <v>0</v>
-      </c>
-      <c r="I852" t="n">
-        <v>0</v>
-      </c>
-      <c r="J852" t="n">
-        <v>0</v>
-      </c>
-      <c r="K852" t="n">
-        <v>0</v>
-      </c>
-      <c r="L852" t="n">
-        <v>0</v>
-      </c>
-      <c r="M852" t="n">
-        <v>0</v>
-      </c>
-      <c r="N852" t="n">
-        <v>0</v>
-      </c>
-      <c r="O852" t="n">
-        <v>0</v>
-      </c>
-      <c r="P852" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q852" t="n">
-        <v>0</v>
-      </c>
-      <c r="R852" s="2" t="inlineStr"/>
-      <c r="U852">
+      <c r="H853" t="n">
+        <v>0</v>
+      </c>
+      <c r="I853" t="n">
+        <v>0</v>
+      </c>
+      <c r="J853" t="n">
+        <v>0</v>
+      </c>
+      <c r="K853" t="n">
+        <v>0</v>
+      </c>
+      <c r="L853" t="n">
+        <v>0</v>
+      </c>
+      <c r="M853" t="n">
+        <v>0</v>
+      </c>
+      <c r="N853" t="n">
+        <v>0</v>
+      </c>
+      <c r="O853" t="n">
+        <v>0</v>
+      </c>
+      <c r="P853" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q853" t="n">
+        <v>0</v>
+      </c>
+      <c r="R853" s="2" t="inlineStr"/>
+      <c r="U853">
         <f>HYPERLINK("https://klasma.github.io/Logging_1981/knärot/A 53951-2023 karta knärot.png", "A 53951-2023")</f>
         <v/>
       </c>
-      <c r="V852">
+      <c r="V853">
         <f>HYPERLINK("https://klasma.github.io/Logging_1981/klagomål/A 53951-2023 FSC-klagomål.docx", "A 53951-2023")</f>
         <v/>
       </c>
-      <c r="W852">
+      <c r="W853">
         <f>HYPERLINK("https://klasma.github.io/Logging_1981/klagomålsmail/A 53951-2023 FSC-klagomål mail.docx", "A 53951-2023")</f>
         <v/>
       </c>
-      <c r="X852">
+      <c r="X853">
         <f>HYPERLINK("https://klasma.github.io/Logging_1981/tillsyn/A 53951-2023 tillsynsbegäran.docx", "A 53951-2023")</f>
         <v/>
       </c>
-      <c r="Y852">
+      <c r="Y853">
         <f>HYPERLINK("https://klasma.github.io/Logging_1981/tillsynsmail/A 53951-2023 tillsynsbegäran mail.docx", "A 53951-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="853" ht="15" customHeight="1">
-      <c r="A853" t="inlineStr">
-        <is>
-          <t>A 53877-2023</t>
-        </is>
-      </c>
-      <c r="B853" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="C853" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>SALA</t>
-        </is>
-      </c>
-      <c r="G853" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H853" t="n">
-        <v>0</v>
-      </c>
-      <c r="I853" t="n">
-        <v>0</v>
-      </c>
-      <c r="J853" t="n">
-        <v>0</v>
-      </c>
-      <c r="K853" t="n">
-        <v>0</v>
-      </c>
-      <c r="L853" t="n">
-        <v>0</v>
-      </c>
-      <c r="M853" t="n">
-        <v>0</v>
-      </c>
-      <c r="N853" t="n">
-        <v>0</v>
-      </c>
-      <c r="O853" t="n">
-        <v>0</v>
-      </c>
-      <c r="P853" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q853" t="n">
-        <v>0</v>
-      </c>
-      <c r="R853" s="2" t="inlineStr"/>
-    </row>
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51186,14 +51186,14 @@
     <row r="859" ht="15" customHeight="1">
       <c r="A859" t="inlineStr">
         <is>
-          <t>A 56064-2023</t>
+          <t>A 56057-2023</t>
         </is>
       </c>
       <c r="B859" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 56057-2023</t>
+          <t>A 56064-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51357,14 +51357,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 55474-2023</t>
+          <t>A 55504-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -51414,14 +51414,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 55504-2023</t>
+          <t>A 55474-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51528,14 +51528,14 @@
     <row r="865" ht="15" customHeight="1">
       <c r="A865" t="inlineStr">
         <is>
-          <t>A 56949-2023</t>
+          <t>A 56956-2023</t>
         </is>
       </c>
       <c r="B865" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -51585,14 +51585,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 56956-2023</t>
+          <t>A 56964-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -51642,14 +51642,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 56964-2023</t>
+          <t>A 56949-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50901,14 +50901,14 @@
     <row r="854" ht="15" customHeight="1">
       <c r="A854" t="inlineStr">
         <is>
-          <t>A 54114-2023</t>
+          <t>A 54125-2023</t>
         </is>
       </c>
       <c r="B854" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         </is>
       </c>
       <c r="G854" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -50958,14 +50958,14 @@
     <row r="855" ht="15" customHeight="1">
       <c r="A855" t="inlineStr">
         <is>
-          <t>A 54118-2023</t>
+          <t>A 54114-2023</t>
         </is>
       </c>
       <c r="B855" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         </is>
       </c>
       <c r="G855" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -51015,14 +51015,14 @@
     <row r="856" ht="15" customHeight="1">
       <c r="A856" t="inlineStr">
         <is>
-          <t>A 54125-2023</t>
+          <t>A 54118-2023</t>
         </is>
       </c>
       <c r="B856" s="1" t="n">
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         </is>
       </c>
       <c r="G856" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="H856" t="n">
         <v>0</v>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51186,14 +51186,14 @@
     <row r="859" ht="15" customHeight="1">
       <c r="A859" t="inlineStr">
         <is>
-          <t>A 56057-2023</t>
+          <t>A 56064-2023</t>
         </is>
       </c>
       <c r="B859" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 56064-2023</t>
+          <t>A 56057-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51357,14 +51357,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 55504-2023</t>
+          <t>A 55474-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -51414,14 +51414,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 55474-2023</t>
+          <t>A 55504-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51528,14 +51528,14 @@
     <row r="865" ht="15" customHeight="1">
       <c r="A865" t="inlineStr">
         <is>
-          <t>A 56956-2023</t>
+          <t>A 56949-2023</t>
         </is>
       </c>
       <c r="B865" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -51585,14 +51585,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 56964-2023</t>
+          <t>A 56956-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -51642,14 +51642,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 56949-2023</t>
+          <t>A 56964-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51186,14 +51186,14 @@
     <row r="859" ht="15" customHeight="1">
       <c r="A859" t="inlineStr">
         <is>
-          <t>A 56064-2023</t>
+          <t>A 56057-2023</t>
         </is>
       </c>
       <c r="B859" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         </is>
       </c>
       <c r="G859" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -51243,14 +51243,14 @@
     <row r="860" ht="15" customHeight="1">
       <c r="A860" t="inlineStr">
         <is>
-          <t>A 56057-2023</t>
+          <t>A 56064-2023</t>
         </is>
       </c>
       <c r="B860" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         </is>
       </c>
       <c r="G860" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51357,14 +51357,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 55474-2023</t>
+          <t>A 55504-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -51414,14 +51414,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 55504-2023</t>
+          <t>A 55474-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51357,14 +51357,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 55504-2023</t>
+          <t>A 55474-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -51414,14 +51414,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 55474-2023</t>
+          <t>A 55504-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51528,14 +51528,14 @@
     <row r="865" ht="15" customHeight="1">
       <c r="A865" t="inlineStr">
         <is>
-          <t>A 56949-2023</t>
+          <t>A 56956-2023</t>
         </is>
       </c>
       <c r="B865" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -51585,14 +51585,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 56956-2023</t>
+          <t>A 56964-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -51642,14 +51642,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 56964-2023</t>
+          <t>A 56949-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52041,14 +52041,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 59785-2023</t>
+          <t>A 59713-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -52098,14 +52098,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 59713-2023</t>
+          <t>A 59785-2023</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51357,14 +51357,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 55474-2023</t>
+          <t>A 55504-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -51414,14 +51414,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 55504-2023</t>
+          <t>A 55474-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y876"/>
+  <dimension ref="A1:Y877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51528,14 +51528,14 @@
     <row r="865" ht="15" customHeight="1">
       <c r="A865" t="inlineStr">
         <is>
-          <t>A 56956-2023</t>
+          <t>A 56949-2023</t>
         </is>
       </c>
       <c r="B865" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -51585,14 +51585,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 56964-2023</t>
+          <t>A 56956-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -51642,14 +51642,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 56949-2023</t>
+          <t>A 56964-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52041,14 +52041,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 59713-2023</t>
+          <t>A 59785-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -52098,14 +52098,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 59785-2023</t>
+          <t>A 59713-2023</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -52152,7 +52152,7 @@
       </c>
       <c r="R875" s="2" t="inlineStr"/>
     </row>
-    <row r="876">
+    <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
           <t>A 60249-2023</t>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52208,6 +52208,63 @@
         <v>0</v>
       </c>
       <c r="R876" s="2" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>A 61525-2023</t>
+        </is>
+      </c>
+      <c r="B877" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="C877" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>SALA</t>
+        </is>
+      </c>
+      <c r="G877" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H877" t="n">
+        <v>0</v>
+      </c>
+      <c r="I877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J877" t="n">
+        <v>0</v>
+      </c>
+      <c r="K877" t="n">
+        <v>0</v>
+      </c>
+      <c r="L877" t="n">
+        <v>0</v>
+      </c>
+      <c r="M877" t="n">
+        <v>0</v>
+      </c>
+      <c r="N877" t="n">
+        <v>0</v>
+      </c>
+      <c r="O877" t="n">
+        <v>0</v>
+      </c>
+      <c r="P877" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q877" t="n">
+        <v>0</v>
+      </c>
+      <c r="R877" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51357,14 +51357,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 55504-2023</t>
+          <t>A 55474-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -51414,14 +51414,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 55474-2023</t>
+          <t>A 55504-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>45265</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y877"/>
+  <dimension ref="A1:Y879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51357,14 +51357,14 @@
     <row r="862" ht="15" customHeight="1">
       <c r="A862" t="inlineStr">
         <is>
-          <t>A 55474-2023</t>
+          <t>A 55504-2023</t>
         </is>
       </c>
       <c r="B862" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         </is>
       </c>
       <c r="G862" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -51414,14 +51414,14 @@
     <row r="863" ht="15" customHeight="1">
       <c r="A863" t="inlineStr">
         <is>
-          <t>A 55504-2023</t>
+          <t>A 55474-2023</t>
         </is>
       </c>
       <c r="B863" s="1" t="n">
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         </is>
       </c>
       <c r="G863" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H863" t="n">
         <v>0</v>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51528,14 +51528,14 @@
     <row r="865" ht="15" customHeight="1">
       <c r="A865" t="inlineStr">
         <is>
-          <t>A 56949-2023</t>
+          <t>A 56956-2023</t>
         </is>
       </c>
       <c r="B865" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -51585,14 +51585,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 56956-2023</t>
+          <t>A 56964-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -51642,14 +51642,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 56964-2023</t>
+          <t>A 56949-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52041,14 +52041,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 59785-2023</t>
+          <t>A 59713-2023</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -52098,14 +52098,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 59713-2023</t>
+          <t>A 59785-2023</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52209,62 +52209,176 @@
       </c>
       <c r="R876" s="2" t="inlineStr"/>
     </row>
-    <row r="877">
+    <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
+          <t>A 60731-2023</t>
+        </is>
+      </c>
+      <c r="B877" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C877" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>SALA</t>
+        </is>
+      </c>
+      <c r="G877" t="n">
+        <v>1</v>
+      </c>
+      <c r="H877" t="n">
+        <v>0</v>
+      </c>
+      <c r="I877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J877" t="n">
+        <v>0</v>
+      </c>
+      <c r="K877" t="n">
+        <v>0</v>
+      </c>
+      <c r="L877" t="n">
+        <v>0</v>
+      </c>
+      <c r="M877" t="n">
+        <v>0</v>
+      </c>
+      <c r="N877" t="n">
+        <v>0</v>
+      </c>
+      <c r="O877" t="n">
+        <v>0</v>
+      </c>
+      <c r="P877" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q877" t="n">
+        <v>0</v>
+      </c>
+      <c r="R877" s="2" t="inlineStr"/>
+    </row>
+    <row r="878" ht="15" customHeight="1">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>A 60730-2023</t>
+        </is>
+      </c>
+      <c r="B878" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C878" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>SALA</t>
+        </is>
+      </c>
+      <c r="G878" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H878" t="n">
+        <v>0</v>
+      </c>
+      <c r="I878" t="n">
+        <v>0</v>
+      </c>
+      <c r="J878" t="n">
+        <v>0</v>
+      </c>
+      <c r="K878" t="n">
+        <v>0</v>
+      </c>
+      <c r="L878" t="n">
+        <v>0</v>
+      </c>
+      <c r="M878" t="n">
+        <v>0</v>
+      </c>
+      <c r="N878" t="n">
+        <v>0</v>
+      </c>
+      <c r="O878" t="n">
+        <v>0</v>
+      </c>
+      <c r="P878" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q878" t="n">
+        <v>0</v>
+      </c>
+      <c r="R878" s="2" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
           <t>A 61525-2023</t>
         </is>
       </c>
-      <c r="B877" s="1" t="n">
+      <c r="B879" s="1" t="n">
         <v>45265</v>
       </c>
-      <c r="C877" s="1" t="n">
-        <v>45267</v>
-      </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E877" t="inlineStr">
-        <is>
-          <t>SALA</t>
-        </is>
-      </c>
-      <c r="G877" t="n">
+      <c r="C879" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>SALA</t>
+        </is>
+      </c>
+      <c r="G879" t="n">
         <v>1.6</v>
       </c>
-      <c r="H877" t="n">
-        <v>0</v>
-      </c>
-      <c r="I877" t="n">
-        <v>0</v>
-      </c>
-      <c r="J877" t="n">
-        <v>0</v>
-      </c>
-      <c r="K877" t="n">
-        <v>0</v>
-      </c>
-      <c r="L877" t="n">
-        <v>0</v>
-      </c>
-      <c r="M877" t="n">
-        <v>0</v>
-      </c>
-      <c r="N877" t="n">
-        <v>0</v>
-      </c>
-      <c r="O877" t="n">
-        <v>0</v>
-      </c>
-      <c r="P877" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q877" t="n">
-        <v>0</v>
-      </c>
-      <c r="R877" s="2" t="inlineStr"/>
+      <c r="H879" t="n">
+        <v>0</v>
+      </c>
+      <c r="I879" t="n">
+        <v>0</v>
+      </c>
+      <c r="J879" t="n">
+        <v>0</v>
+      </c>
+      <c r="K879" t="n">
+        <v>0</v>
+      </c>
+      <c r="L879" t="n">
+        <v>0</v>
+      </c>
+      <c r="M879" t="n">
+        <v>0</v>
+      </c>
+      <c r="N879" t="n">
+        <v>0</v>
+      </c>
+      <c r="O879" t="n">
+        <v>0</v>
+      </c>
+      <c r="P879" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q879" t="n">
+        <v>0</v>
+      </c>
+      <c r="R879" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y879"/>
+  <dimension ref="A1:Y880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44694</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>44694</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44699</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44699</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44701</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44708</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>44713</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44713</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44713</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44715</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44719</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>44719</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44719</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44722</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44722</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44727</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44727</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44728</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44732</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44732</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44741</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>44741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>44742</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>44742</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44742</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44746</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44746</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44747</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44749</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44749</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44749</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44749</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44749</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44749</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44749</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44749</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44750</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>44750</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44750</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>44750</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44750</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44750</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44750</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44756</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>44756</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44756</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>44760</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44761</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>44768</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>44768</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44774</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44774</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44774</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44774</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44788</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44791</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44792</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44795</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44798</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>44799</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44811</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44812</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44818</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44818</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44818</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44819</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44819</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>44819</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44823</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44823</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>44827</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44830</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>44831</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44831</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44831</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44833</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44833</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44837</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>44839</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44839</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44839</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>44841</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>44841</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>44841</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44844</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44845</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>44845</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>44847</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44848</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44854</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44854</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44855</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44858</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44860</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44861</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44861</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44861</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44866</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44866</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44867</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44871</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>44871</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44874</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44874</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44874</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44879</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44879</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44879</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44879</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44880</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44880</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44880</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44881</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44888</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44889</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44890</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44890</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44893</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44893</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44893</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>44893</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>44893</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44896</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44900</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44902</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44902</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44904</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44907</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44910</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44912</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44914</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44917</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>44917</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44917</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>44918</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44923</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>44935</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>44937</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44937</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44939</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44939</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44943</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44943</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44951</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44951</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44951</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44957</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44957</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44957</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44957</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44957</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44964</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44964</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44964</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44964</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44964</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44964</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44964</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44965</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>44967</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>44970</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44970</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44970</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44971</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44971</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44971</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>44972</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>44972</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44973</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>44973</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>44973</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44974</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44978</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>44979</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44992</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>44992</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>44992</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>44994</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>44995</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44995</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>44995</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44995</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>44995</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44995</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>45000</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45000</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45002</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45002</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45002</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45002</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45002</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45002</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45007</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45007</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45007</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45007</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45007</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>45008</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45013</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45014</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45014</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45014</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45020</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45020</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45024</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45024</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45027</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45027</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42260,7 +42260,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45029</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45029</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45029</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45029</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45029</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45034</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45034</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45034</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45034</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45040</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45042</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45044</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45054</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45055</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45055</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45056</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45057</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45058</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45069</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45069</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45069</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45069</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45070</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45072</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45072</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45075</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45075</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45075</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45075</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45075</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45076</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45077</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45079</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45082</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45083</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45083</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45083</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45084</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45084</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45085</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45086</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45086</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45086</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45089</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45089</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45089</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45089</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45090</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45090</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45092</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45092</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45092</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45092</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45092</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45093</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45093</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45094</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45095</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45096</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45096</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45097</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45097</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45097</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45098</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45098</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45098</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45107</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45107</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45107</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45114</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45117</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>45126</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45126</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45131</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45131</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45133</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45133</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45133</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45138</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45141</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45142</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45146</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48075,7 +48075,7 @@
         <v>45152</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45154</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45161</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45162</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>45162</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45163</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45167</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45167</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>45167</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>45169</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45173</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45173</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>45175</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45179</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45179</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45179</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45182</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45183</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45183</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45183</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45183</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45183</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45183</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45183</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45184</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45184</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45188</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45190</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45190</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45192</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45192</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45192</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>45194</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>45194</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50023,7 +50023,7 @@
         <v>45195</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45196</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45202</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>45211</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>45216</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45219</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45223</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45225</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45229</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45229</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45229</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45229</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45229</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45231</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45231</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45232</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45232</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45232</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45232</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45232</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45233</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45233</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>45236</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>45238</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45240</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51528,14 +51528,14 @@
     <row r="865" ht="15" customHeight="1">
       <c r="A865" t="inlineStr">
         <is>
-          <t>A 56956-2023</t>
+          <t>A 56949-2023</t>
         </is>
       </c>
       <c r="B865" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         </is>
       </c>
       <c r="G865" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -51585,14 +51585,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 56964-2023</t>
+          <t>A 56956-2023</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -51642,14 +51642,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 56949-2023</t>
+          <t>A 56964-2023</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -51706,7 +51706,7 @@
         <v>45247</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45249</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51820,7 +51820,7 @@
         <v>45250</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51877,7 +51877,7 @@
         <v>45252</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45252</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45253</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45257</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45257</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>45258</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52212,14 +52212,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 60731-2023</t>
+          <t>A 60730-2023</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52232,7 +52232,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -52269,14 +52269,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 60730-2023</t>
+          <t>A 60731-2023</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52289,7 +52289,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -52323,7 +52323,7 @@
       </c>
       <c r="R878" s="2" t="inlineStr"/>
     </row>
-    <row r="879">
+    <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
           <t>A 61525-2023</t>
@@ -52333,7 +52333,7 @@
         <v>45265</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52379,6 +52379,63 @@
         <v>0</v>
       </c>
       <c r="R879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>A 62449-2023</t>
+        </is>
+      </c>
+      <c r="B880" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="C880" s="1" t="n">
+        <v>45269</v>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>SALA</t>
+        </is>
+      </c>
+      <c r="G880" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H880" t="n">
+        <v>0</v>
+      </c>
+      <c r="I880" t="n">
+        <v>0</v>
+      </c>
+      <c r="J880" t="n">
+        <v>0</v>
+      </c>
+      <c r="K880" t="n">
+        <v>0</v>
+      </c>
+      <c r="L880" t="n">
+        <v>0</v>
+      </c>
+      <c r="M880" t="n">
+        <v>0</v>
+      </c>
+      <c r="N880" t="n">
+        <v>0</v>
+      </c>
+      <c r="O880" t="n">
+        <v>0</v>
+      </c>
+      <c r="P880" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q880" t="n">
+        <v>0</v>
+      </c>
+      <c r="R880" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -564,7 +564,7 @@
         <v>44995</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>45188</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44855</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>43640</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>44404</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44127</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44572</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44349</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45097</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>43807</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>44504</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>43410</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>43662</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>43775</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44473</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44552</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44875</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>45001</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45097</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45257</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>43356</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>43502</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43529</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43875</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44020</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44067</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44067</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44132</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44277</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44608</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>44756</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>44973</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45075</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45116</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45183</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>43334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>43361</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>43362</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>43362</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>43377</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>43410</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>43423</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>43424</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>43430</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>43431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>43432</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>43438</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>43439</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>43445</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>43446</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>43451</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>43453</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>43461</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>43461</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>43472</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43474</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>43482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>43485</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>43488</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>43488</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>43496</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>43502</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>43502</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>43502</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43503</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43504</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>43507</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>43510</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>43510</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>43523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>43527</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>43532</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>43536</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>43537</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43538</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>43543</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>43543</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>43548</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>43553</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>43553</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>43558</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>43559</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>43562</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>43563</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43567</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43584</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43585</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>43591</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>43602</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43613</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43614</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43614</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>43621</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>43621</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>43621</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>43628</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43629</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>43635</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>43639</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>43648</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>43664</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>43668</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>43670</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>43671</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>43677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>43679</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>43686</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>43691</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>43698</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>43707</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>43719</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>43724</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>43727</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43728</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43739</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43739</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43741</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43746</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>43752</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>43768</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>43769</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>43769</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>43773</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>43774</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>43775</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43777</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>43777</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43783</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43783</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43784</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43788</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43791</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43794</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43794</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43796</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43796</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43801</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43807</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43808</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>43812</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>43818</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>43818</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>43822</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43832</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43833</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>43833</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>43837</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>43837</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>43839</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>43841</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>43843</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>43846</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>43847</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>43851</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>43853</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>43859</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43860</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>43860</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>43860</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>43860</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43861</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43864</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43865</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43868</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43882</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43885</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43888</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43900</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43903</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43903</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43903</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43906</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43908</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43914</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43915</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43915</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43916</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43922</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43922</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43923</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43923</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43924</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>43936</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>43959</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>43976</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>43978</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>43985</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>43987</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>43990</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>43994</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44005</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44005</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44018</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44018</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44018</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44018</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44021</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44032</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44032</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44054</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44054</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44054</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44061</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44061</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44064</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44067</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44076</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44076</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>44076</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44081</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44085</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44088</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>44096</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44096</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44097</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>44110</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44126</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44127</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44127</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44130</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44132</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44132</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44132</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44145</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44146</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44146</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44156</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44158</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44161</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>44172</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44179</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44182</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44191</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>44191</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44191</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44193</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44193</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44193</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44209</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44214</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44225</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44232</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44235</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44242</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44243</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44243</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44244</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44256</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44259</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44260</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>44260</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>44264</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44272</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44277</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44277</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44284</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44285</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44285</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44294</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44301</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44302</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44305</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44305</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44305</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44308</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44321</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44321</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44323</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>44323</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>44323</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44340</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44340</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44340</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44348</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44348</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44348</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44348</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44356</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44363</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44365</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>44365</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44365</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44365</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44365</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44368</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>44368</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>44369</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44369</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44370</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>44378</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44383</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44384</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44384</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44384</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44384</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44384</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44388</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44400</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44403</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44403</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44403</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44405</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44410</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44414</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44417</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44418</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44418</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44419</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44420</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>44421</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44424</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44425</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44432</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44433</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44438</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44442</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44448</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44448</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44449</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44460</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44470</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44473</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44482</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44482</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44483</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44483</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44487</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44487</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44488</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44489</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>44495</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44497</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44502</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44502</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44502</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44504</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44504</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>44504</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>44504</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44505</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44505</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44512</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44515</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44515</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>44515</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44515</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44517</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44517</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44517</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>44519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44522</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44522</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>44522</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44525</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44525</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44525</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44528</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44529</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44529</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44530</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44531</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44531</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44535</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44536</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44537</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44538</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44540</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44543</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44544</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44545</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44545</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44546</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44546</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44546</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44547</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44550</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44550</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44550</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44551</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44551</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44552</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>44552</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44552</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44552</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44552</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44552</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>44552</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44552</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44557</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44558</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44567</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44571</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44571</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44572</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44573</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44575</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44575</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44579</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44582</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44582</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44586</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>44587</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44587</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44588</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44588</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44592</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44594</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44596</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44596</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44599</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44602</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44602</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44602</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44602</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44603</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44604</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44609</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44615</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44615</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44615</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44616</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44620</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44621</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44622</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44623</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44624</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44624</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44630</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44637</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44648</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44650</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44664</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>44664</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44664</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44670</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44671</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>44673</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>44676</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>44691</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44691</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c